--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ91"/>
+  <dimension ref="A1:AZ92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7926,10 +7926,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127898594</v>
+        <v>136755905</v>
       </c>
       <c r="B67" t="n">
-        <v>56845</v>
+        <v>56939</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7937,21 +7937,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100053</v>
+        <v>100041</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Erinaceus europaeus</t>
+          <t>Coronella austriaca</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Laurenti, 1768</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -7959,6 +7959,18 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -7966,17 +7978,17 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Elljusspår, 146 38 Botkyrka kommun, Srm</t>
+          <t>Brantbrink, Srm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>665529</v>
+        <v>665510</v>
       </c>
       <c r="R67" t="n">
-        <v>6564827</v>
+        <v>6564899</v>
       </c>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8000,22 +8012,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8028,55 +8040,41 @@
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>Johan Möller</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>Via Johan Möller</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr">
-        <is>
-          <t>WWF - Tillsammans för Sveriges igelkottar</t>
-        </is>
-      </c>
+      <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127898594</t>
+          <t>https://artportalen.se/Sighting/136755905</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129052185</v>
+        <v>127898594</v>
       </c>
       <c r="B68" t="n">
-        <v>58114</v>
+        <v>56845</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>100053</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -8084,27 +8082,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Brantbrink, Brantbrink, Srm</t>
+          <t>Elljusspår, 146 38 Botkyrka kommun, Srm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>665290</v>
+        <v>665529</v>
       </c>
       <c r="R68" t="n">
-        <v>6564770</v>
+        <v>6564827</v>
       </c>
       <c r="S68" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8128,22 +8123,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8158,24 +8153,28 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Johan Möller</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
+          <t>Via Johan Möller</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>WWF - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129052185</t>
+          <t>https://artportalen.se/Sighting/127898594</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129107649</v>
+        <v>129052185</v>
       </c>
       <c r="B69" t="n">
         <v>58114</v>
@@ -8203,20 +8202,32 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Brantbrink, Srm</t>
+          <t>Brantbrink, Brantbrink, Srm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>665272</v>
+        <v>665290</v>
       </c>
       <c r="R69" t="n">
-        <v>6564714</v>
+        <v>6564770</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8243,9 +8254,19 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8260,24 +8281,24 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129107649</t>
+          <t>https://artportalen.se/Sighting/129052185</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129150556</v>
+        <v>129107649</v>
       </c>
       <c r="B70" t="n">
         <v>58114</v>
@@ -8306,20 +8327,16 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Brantbrink, Srm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>665406</v>
+        <v>665272</v>
       </c>
       <c r="R70" t="n">
-        <v>6564548</v>
+        <v>6564714</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8346,22 +8363,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8376,62 +8383,66 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129150556</t>
+          <t>https://artportalen.se/Sighting/129107649</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128970284</v>
+        <v>129150556</v>
       </c>
       <c r="B71" t="n">
-        <v>8455</v>
+        <v>58114</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Brantbrink, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>665545</v>
+        <v>665406</v>
       </c>
       <c r="R71" t="n">
-        <v>6564914</v>
+        <v>6564548</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8458,22 +8469,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8499,13 +8510,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128970284</t>
+          <t>https://artportalen.se/Sighting/129150556</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129150615</v>
+        <v>128970284</v>
       </c>
       <c r="B72" t="n">
         <v>8455</v>
@@ -8540,10 +8551,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>665164</v>
+        <v>665545</v>
       </c>
       <c r="R72" t="n">
-        <v>6564505</v>
+        <v>6564914</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8570,22 +8581,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8611,13 +8622,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129150615</t>
+          <t>https://artportalen.se/Sighting/128970284</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129150616</v>
+        <v>129150615</v>
       </c>
       <c r="B73" t="n">
         <v>8455</v>
@@ -8652,10 +8663,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>665382</v>
+        <v>665164</v>
       </c>
       <c r="R73" t="n">
-        <v>6564609</v>
+        <v>6564505</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8687,7 +8698,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8697,7 +8708,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8723,13 +8734,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129150616</t>
+          <t>https://artportalen.se/Sighting/129150615</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129150617</v>
+        <v>129150616</v>
       </c>
       <c r="B74" t="n">
         <v>8455</v>
@@ -8764,10 +8775,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>665376</v>
+        <v>665382</v>
       </c>
       <c r="R74" t="n">
-        <v>6564598</v>
+        <v>6564609</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8799,7 +8810,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8809,7 +8820,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8835,13 +8846,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129150617</t>
+          <t>https://artportalen.se/Sighting/129150616</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129150618</v>
+        <v>129150617</v>
       </c>
       <c r="B75" t="n">
         <v>8455</v>
@@ -8876,10 +8887,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>665400</v>
+        <v>665376</v>
       </c>
       <c r="R75" t="n">
-        <v>6564742</v>
+        <v>6564598</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8911,7 +8922,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8921,7 +8932,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8947,13 +8958,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129150618</t>
+          <t>https://artportalen.se/Sighting/129150617</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129150619</v>
+        <v>129150618</v>
       </c>
       <c r="B76" t="n">
         <v>8455</v>
@@ -8988,10 +8999,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>665365</v>
+        <v>665400</v>
       </c>
       <c r="R76" t="n">
-        <v>6564786</v>
+        <v>6564742</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9023,7 +9034,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9033,7 +9044,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9059,13 +9070,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129150619</t>
+          <t>https://artportalen.se/Sighting/129150618</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129150620</v>
+        <v>129150619</v>
       </c>
       <c r="B77" t="n">
         <v>8455</v>
@@ -9100,10 +9111,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>665358</v>
+        <v>665365</v>
       </c>
       <c r="R77" t="n">
-        <v>6564768</v>
+        <v>6564786</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9135,7 +9146,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9145,7 +9156,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9171,13 +9182,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129150620</t>
+          <t>https://artportalen.se/Sighting/129150619</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129150621</v>
+        <v>129150620</v>
       </c>
       <c r="B78" t="n">
         <v>8455</v>
@@ -9212,10 +9223,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>665321</v>
+        <v>665358</v>
       </c>
       <c r="R78" t="n">
-        <v>6564753</v>
+        <v>6564768</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9247,7 +9258,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9257,7 +9268,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9283,13 +9294,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129150621</t>
+          <t>https://artportalen.se/Sighting/129150620</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129150622</v>
+        <v>129150621</v>
       </c>
       <c r="B79" t="n">
         <v>8455</v>
@@ -9324,10 +9335,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>665194</v>
+        <v>665321</v>
       </c>
       <c r="R79" t="n">
-        <v>6564740</v>
+        <v>6564753</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9359,7 +9370,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9369,7 +9380,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9395,13 +9406,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129150622</t>
+          <t>https://artportalen.se/Sighting/129150621</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129150623</v>
+        <v>129150622</v>
       </c>
       <c r="B80" t="n">
         <v>8455</v>
@@ -9436,10 +9447,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>665233</v>
+        <v>665194</v>
       </c>
       <c r="R80" t="n">
-        <v>6564720</v>
+        <v>6564740</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9471,7 +9482,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9481,7 +9492,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9507,38 +9518,38 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129150623</t>
+          <t>https://artportalen.se/Sighting/129150622</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128970264</v>
+        <v>129150623</v>
       </c>
       <c r="B81" t="n">
-        <v>91930</v>
+        <v>8455</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9548,10 +9559,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>665464</v>
+        <v>665233</v>
       </c>
       <c r="R81" t="n">
-        <v>6565020</v>
+        <v>6564720</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9578,22 +9589,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9619,16 +9630,16 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128970264</t>
+          <t>https://artportalen.se/Sighting/129150623</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128970265</v>
+        <v>128970264</v>
       </c>
       <c r="B82" t="n">
-        <v>93223</v>
+        <v>91930</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9636,21 +9647,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5448</v>
+        <v>5442</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9660,10 +9671,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>665424</v>
+        <v>665464</v>
       </c>
       <c r="R82" t="n">
-        <v>6565096</v>
+        <v>6565020</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9695,7 +9706,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9705,7 +9716,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9731,16 +9742,16 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128970265</t>
+          <t>https://artportalen.se/Sighting/128970264</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128970273</v>
+        <v>128970265</v>
       </c>
       <c r="B83" t="n">
-        <v>93235</v>
+        <v>93223</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9748,21 +9759,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9772,10 +9783,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>665465</v>
+        <v>665424</v>
       </c>
       <c r="R83" t="n">
-        <v>6565043</v>
+        <v>6565096</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9807,7 +9818,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9817,7 +9828,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9843,13 +9854,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128970273</t>
+          <t>https://artportalen.se/Sighting/128970265</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128970274</v>
+        <v>128970273</v>
       </c>
       <c r="B84" t="n">
         <v>93235</v>
@@ -9884,10 +9895,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>665452</v>
+        <v>665465</v>
       </c>
       <c r="R84" t="n">
-        <v>6565050</v>
+        <v>6565043</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9919,7 +9930,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9929,7 +9940,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9955,13 +9966,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128970274</t>
+          <t>https://artportalen.se/Sighting/128970273</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128970275</v>
+        <v>128970274</v>
       </c>
       <c r="B85" t="n">
         <v>93235</v>
@@ -9996,10 +10007,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>665443</v>
+        <v>665452</v>
       </c>
       <c r="R85" t="n">
-        <v>6565057</v>
+        <v>6565050</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10031,7 +10042,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10041,7 +10052,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10067,13 +10078,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128970275</t>
+          <t>https://artportalen.se/Sighting/128970274</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128970277</v>
+        <v>128970275</v>
       </c>
       <c r="B86" t="n">
         <v>93235</v>
@@ -10108,10 +10119,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>665424</v>
+        <v>665443</v>
       </c>
       <c r="R86" t="n">
-        <v>6565079</v>
+        <v>6565057</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10143,7 +10154,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10153,7 +10164,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10179,13 +10190,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128970277</t>
+          <t>https://artportalen.se/Sighting/128970275</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128970278</v>
+        <v>128970277</v>
       </c>
       <c r="B87" t="n">
         <v>93235</v>
@@ -10220,10 +10231,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>665427</v>
+        <v>665424</v>
       </c>
       <c r="R87" t="n">
-        <v>6565093</v>
+        <v>6565079</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10255,7 +10266,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10265,7 +10276,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10291,13 +10302,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128970278</t>
+          <t>https://artportalen.se/Sighting/128970277</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128970279</v>
+        <v>128970278</v>
       </c>
       <c r="B88" t="n">
         <v>93235</v>
@@ -10332,10 +10343,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>665487</v>
+        <v>665427</v>
       </c>
       <c r="R88" t="n">
-        <v>6565071</v>
+        <v>6565093</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10367,7 +10378,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10377,7 +10388,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10403,13 +10414,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128970279</t>
+          <t>https://artportalen.se/Sighting/128970278</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128970280</v>
+        <v>128970279</v>
       </c>
       <c r="B89" t="n">
         <v>93235</v>
@@ -10444,10 +10455,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>665491</v>
+        <v>665487</v>
       </c>
       <c r="R89" t="n">
-        <v>6565068</v>
+        <v>6565071</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10479,7 +10490,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10489,7 +10500,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10515,13 +10526,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128970280</t>
+          <t>https://artportalen.se/Sighting/128970279</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128970281</v>
+        <v>128970280</v>
       </c>
       <c r="B90" t="n">
         <v>93235</v>
@@ -10556,10 +10567,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>665505</v>
+        <v>665491</v>
       </c>
       <c r="R90" t="n">
-        <v>6565027</v>
+        <v>6565068</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10591,7 +10602,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10601,7 +10612,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10627,13 +10638,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128970281</t>
+          <t>https://artportalen.se/Sighting/128970280</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128970282</v>
+        <v>128970281</v>
       </c>
       <c r="B91" t="n">
         <v>93235</v>
@@ -10668,10 +10679,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>665516</v>
+        <v>665505</v>
       </c>
       <c r="R91" t="n">
-        <v>6565017</v>
+        <v>6565027</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10703,7 +10714,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10713,7 +10724,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10738,6 +10749,118 @@
       </c>
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128970281</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>128970282</v>
+      </c>
+      <c r="B92" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Brantbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>665516</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6565017</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128970282</t>
         </is>
@@ -10835,6 +10958,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -7929,7 +7929,7 @@
         <v>136755905</v>
       </c>
       <c r="B67" t="n">
-        <v>56939</v>
+        <v>56941</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8040,6 +8040,16 @@
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Eva Reynolds</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Eva Reynolds</t>
+        </is>
+      </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -7929,7 +7929,7 @@
         <v>136755905</v>
       </c>
       <c r="B67" t="n">
-        <v>56941</v>
+        <v>56954</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -7929,7 +7929,7 @@
         <v>136755905</v>
       </c>
       <c r="B67" t="n">
-        <v>56954</v>
+        <v>56956</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -7960,17 +7960,9 @@
         </is>
       </c>
       <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
           <t>observerad</t>

--- a/artfynd/A 48514-2025 artfynd.xlsx
+++ b/artfynd/A 48514-2025 artfynd.xlsx
@@ -7929,7 +7929,7 @@
         <v>136755905</v>
       </c>
       <c r="B67" t="n">
-        <v>56956</v>
+        <v>56966</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
